--- a/Soccer_Infrared_2026/Documentation/BOM_Materials_List/BOM_SESI_ChangeMakers_2026.xlsx
+++ b/Soccer_Infrared_2026/Documentation/BOM_Materials_List/BOM_SESI_ChangeMakers_2026.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30602"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D16F902A-7A0F-4521-B1D6-2C7AFB143586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1652D2AA-6570-4D56-9294-379093EE2697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Pt-BR" sheetId="1" r:id="rId1"/>
+    <sheet name="ENG" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="334">
   <si>
     <t>Lista de Materias (BOM) SESI ChangeMakers - Americana, SP</t>
   </si>
@@ -81,148 +82,157 @@
     <t>Personalizado</t>
   </si>
   <si>
+    <t>Fabricação Própria</t>
+  </si>
+  <si>
+    <t>Novo</t>
+  </si>
+  <si>
+    <t>SESI - SP</t>
+  </si>
+  <si>
+    <t>Estrutura principal do robô e suporte dos componentes</t>
+  </si>
+  <si>
+    <t>Motorização</t>
+  </si>
+  <si>
+    <t>Motor DC com caixa de redução</t>
+  </si>
+  <si>
+    <t>Motor 25GA370</t>
+  </si>
+  <si>
+    <t>NEWPORT ROBOTICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kit </t>
+  </si>
+  <si>
+    <t>Responsável pela locomoção do robô</t>
+  </si>
+  <si>
+    <t>Roda omni 50mm</t>
+  </si>
+  <si>
+    <t>Rodas de fabricação própria</t>
+  </si>
+  <si>
+    <t>Permite movimentação omnidirecional</t>
+  </si>
+  <si>
+    <t>Controle Principal</t>
+  </si>
+  <si>
+    <t>Esp32 S3 DevKit</t>
+  </si>
+  <si>
+    <t>Módulo Wifi Bluetooth</t>
+  </si>
+  <si>
+    <t>AUTOCORE</t>
+  </si>
+  <si>
+    <t>Microcontroladores principais do robô</t>
+  </si>
+  <si>
+    <t>Controle Motor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driver de motor </t>
+  </si>
+  <si>
+    <t>Drivers de motor TB6612FNG</t>
+  </si>
+  <si>
+    <t>Controle de velocidade e direção dos motores</t>
+  </si>
+  <si>
+    <t>Sensores de Bola</t>
+  </si>
+  <si>
+    <t>TSOP2240</t>
+  </si>
+  <si>
+    <t>Vishay TSSP4038</t>
+  </si>
+  <si>
+    <t>ROBOCORE TECNOLOGIA</t>
+  </si>
+  <si>
+    <t>Kit</t>
+  </si>
+  <si>
+    <t>Montados na borda da placa circular (IR Seeker)</t>
+  </si>
+  <si>
+    <t>Sensores de Linha</t>
+  </si>
+  <si>
+    <t>Multiplexador 16 canais</t>
+  </si>
+  <si>
+    <t>CD74HC4067</t>
+  </si>
+  <si>
+    <t>Multiplexação dos LDRs</t>
+  </si>
+  <si>
+    <t>Sensor de Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bússola digital </t>
+  </si>
+  <si>
+    <t>Módulo Bússola HMC5883L</t>
+  </si>
+  <si>
+    <t>Para alinhamento em campo</t>
+  </si>
+  <si>
+    <t>Sensor ultrassônico HC-SR04</t>
+  </si>
+  <si>
+    <t>HC-SR04</t>
+  </si>
+  <si>
+    <t>Frente, trás, esquerda, direita</t>
+  </si>
+  <si>
+    <t>Visão Computacional</t>
+  </si>
+  <si>
+    <t>Câmera com microcontrolador</t>
+  </si>
+  <si>
+    <t>OpenMV Cam RT1062</t>
+  </si>
+  <si>
+    <t>OpenMV</t>
+  </si>
+  <si>
+    <t>Processamento visual e identificação de objetos</t>
+  </si>
+  <si>
+    <t>Interface</t>
+  </si>
+  <si>
+    <t>Display OLED</t>
+  </si>
+  <si>
+    <t>0.96” I2C</t>
+  </si>
+  <si>
+    <t>Para debug</t>
+  </si>
+  <si>
+    <t>Botão liga/desliga</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
-    <t>Novo</t>
-  </si>
-  <si>
-    <t>SESI - SP</t>
-  </si>
-  <si>
-    <t>Estrutura principal do robô e suporte dos componentes</t>
-  </si>
-  <si>
-    <t>Motorização</t>
-  </si>
-  <si>
-    <t>Motor DC com caixa de redução</t>
-  </si>
-  <si>
-    <t>Motor 25GA370</t>
-  </si>
-  <si>
-    <t>NEWPORT ROBOTICA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kit </t>
-  </si>
-  <si>
-    <t>Responsável pela locomoção do robô</t>
-  </si>
-  <si>
-    <t>Roda omni 50mm</t>
-  </si>
-  <si>
-    <t>Rodas de fabricação própria</t>
-  </si>
-  <si>
-    <t>Permite movimentação omnidirecional</t>
-  </si>
-  <si>
-    <t>Controle Principal</t>
-  </si>
-  <si>
-    <t>Esp32 S3 DevKit</t>
-  </si>
-  <si>
-    <t>Módulo Wifi Bluetooth</t>
-  </si>
-  <si>
-    <t>AUTOCORE</t>
-  </si>
-  <si>
-    <t>Microcontroladores principais do robô</t>
-  </si>
-  <si>
-    <t>Controle Motor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Driver de motor </t>
-  </si>
-  <si>
-    <t>Drivers de motor TB6612FNG</t>
-  </si>
-  <si>
-    <t>Controle de velocidade e direção dos motores</t>
-  </si>
-  <si>
-    <t>Sensores de Bola</t>
-  </si>
-  <si>
-    <t>TSOP2240</t>
-  </si>
-  <si>
-    <t>Vishay TSOP2240</t>
-  </si>
-  <si>
-    <t>ROBOCORE TECNOLOGIA</t>
-  </si>
-  <si>
-    <t>Kit</t>
-  </si>
-  <si>
-    <t>Montados na borda da placa circular (IR Seeker)</t>
-  </si>
-  <si>
-    <t>Sensores de Linha</t>
-  </si>
-  <si>
-    <t>Multiplexador 16 canais</t>
-  </si>
-  <si>
-    <t>CD74HC4067</t>
-  </si>
-  <si>
-    <t>Multiplexação dos LDRs</t>
-  </si>
-  <si>
-    <t>Sensor de Campo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bússola digital </t>
-  </si>
-  <si>
-    <t>Módulo Bússola HMC5883L</t>
-  </si>
-  <si>
-    <t>Para alinhamento em campo</t>
-  </si>
-  <si>
-    <t>Sensor ultrassônico HC-SR04</t>
-  </si>
-  <si>
-    <t>HC-SR04</t>
-  </si>
-  <si>
-    <t>Frente, trás, esquerda, direita</t>
-  </si>
-  <si>
-    <t>Visão Computacional</t>
-  </si>
-  <si>
-    <t>Câmera com microcontrolador</t>
-  </si>
-  <si>
-    <t>OpenMV Cam RT1062</t>
-  </si>
-  <si>
-    <t>Processamento visual e identificação de objetos</t>
-  </si>
-  <si>
-    <t>Interface</t>
-  </si>
-  <si>
-    <t>Display OLED</t>
-  </si>
-  <si>
-    <t>0.96” I2C</t>
-  </si>
-  <si>
-    <t>Para debug</t>
-  </si>
-  <si>
-    <t>Botão liga/desliga</t>
+    <t>FORTELETRO</t>
   </si>
   <si>
     <t>Uso como chave geral</t>
@@ -571,16 +581,470 @@
   </si>
   <si>
     <t>Custo total do projeto:</t>
+  </si>
+  <si>
+    <t>Bill of Materials (BOM) SESI ChangeMakers - Americana, SP</t>
+  </si>
+  <si>
+    <t>Component Name/Description</t>
+  </si>
+  <si>
+    <t>Quantity (units)</t>
+  </si>
+  <si>
+    <t>Reference/Model</t>
+  </si>
+  <si>
+    <t>Supplier</t>
+  </si>
+  <si>
+    <t>Kit/Customized</t>
+  </si>
+  <si>
+    <t>Unit Price (US$)</t>
+  </si>
+  <si>
+    <t>Subtotal (US$)</t>
+  </si>
+  <si>
+    <t>Supporter</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Mechanical Structure</t>
+  </si>
+  <si>
+    <t>3D-Printed Chassis</t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>In-House Manufacturing</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>Customized</t>
+  </si>
+  <si>
+    <t>Main Robot Structure and Component Mounting Support</t>
+  </si>
+  <si>
+    <t>Motorization</t>
+  </si>
+  <si>
+    <t>DC Geared Motor</t>
+  </si>
+  <si>
+    <t>25GA370 Motor</t>
+  </si>
+  <si>
+    <t>Responsible for Robot Movement</t>
+  </si>
+  <si>
+    <t>50 mm Omni Wheel</t>
+  </si>
+  <si>
+    <t>In-House Manufactured Wheels</t>
+  </si>
+  <si>
+    <t>Enables Omnidirectional Movement</t>
+  </si>
+  <si>
+    <t>Main Control</t>
+  </si>
+  <si>
+    <t>Wi-Fi/Bluetooth Module</t>
+  </si>
+  <si>
+    <t>Main Robot Microcontrollers</t>
+  </si>
+  <si>
+    <t>Motor Control</t>
+  </si>
+  <si>
+    <t>Motor Driver</t>
+  </si>
+  <si>
+    <t>TB6612FNG Motor Drivers</t>
+  </si>
+  <si>
+    <t>Motor Speed and Direction Control</t>
+  </si>
+  <si>
+    <t>Ball Sensors</t>
+  </si>
+  <si>
+    <t>Vishay TSSP4038 IR Receiver</t>
+  </si>
+  <si>
+    <t>Mounted Around the Edge of the Circular Board (IR Seeker)</t>
+  </si>
+  <si>
+    <t>Line Sensors</t>
+  </si>
+  <si>
+    <t>16-Channel Multiplexer</t>
+  </si>
+  <si>
+    <t>LDR Multiplexing</t>
+  </si>
+  <si>
+    <t>Field Sensors</t>
+  </si>
+  <si>
+    <t>Digital Compass</t>
+  </si>
+  <si>
+    <t>HMC5883L Compass Module</t>
+  </si>
+  <si>
+    <t>For Field Alignment</t>
+  </si>
+  <si>
+    <t>HC-SR04 Ultrasonic Sensor</t>
+  </si>
+  <si>
+    <t>Front, Back, Left, Right</t>
+  </si>
+  <si>
+    <t>Computer Vision</t>
+  </si>
+  <si>
+    <t>Camera with Microcontroller</t>
+  </si>
+  <si>
+    <t>Visual Processing and Object Detection</t>
+  </si>
+  <si>
+    <t>OLED Display</t>
+  </si>
+  <si>
+    <t>For Debugging</t>
+  </si>
+  <si>
+    <t>On/Off Switch</t>
+  </si>
+  <si>
+    <t>Used as the Main Power Switch</t>
+  </si>
+  <si>
+    <t>Digital Voltmeter</t>
+  </si>
+  <si>
+    <t>3-Digit 4.5–30 VDC</t>
+  </si>
+  <si>
+    <t>Overall Battery Voltage Monitoring</t>
+  </si>
+  <si>
+    <t>Custom PCB</t>
+  </si>
+  <si>
+    <t>Upper Circular PCB</t>
+  </si>
+  <si>
+    <t>EasyEDA/Custom</t>
+  </si>
+  <si>
+    <t>Structural Support and Electronic Integration</t>
+  </si>
+  <si>
+    <t>Main Circular PCB</t>
+  </si>
+  <si>
+    <t>Main Signal Distribution</t>
+  </si>
+  <si>
+    <t>Kicker Circular PCB</t>
+  </si>
+  <si>
+    <t>Electronic Kicking Mechanism</t>
+  </si>
+  <si>
+    <t>Lower Circular PCB</t>
+  </si>
+  <si>
+    <t>Structural and Electrical Base of the System</t>
+  </si>
+  <si>
+    <t>LDR Photoresistor Sensor</t>
+  </si>
+  <si>
+    <t>White Field Line Detection</t>
+  </si>
+  <si>
+    <t>Power Supply</t>
+  </si>
+  <si>
+    <t>Voltage Regulator Module</t>
+  </si>
+  <si>
+    <t>Mini 560 Step-Down Converter</t>
+  </si>
+  <si>
+    <t>Provides Power to the Main Board</t>
+  </si>
+  <si>
+    <t>Step-Up Converter Module</t>
+  </si>
+  <si>
+    <t>XL6009 Boost Converter</t>
+  </si>
+  <si>
+    <t>Boosts Voltage for the Kicker Board</t>
+  </si>
+  <si>
+    <t>2200 µF Capacitor</t>
+  </si>
+  <si>
+    <t>Voltage Filtering and Stabilization</t>
+  </si>
+  <si>
+    <t>2.2 µF Electrolytic Capacitor</t>
+  </si>
+  <si>
+    <t>2.2 µF 16V Capacitor</t>
+  </si>
+  <si>
+    <t>Reduction of Power Supply Fluctuations and Noise</t>
+  </si>
+  <si>
+    <t>1000 µF Capacitor</t>
+  </si>
+  <si>
+    <t>1000 µF 63V Capacitor</t>
+  </si>
+  <si>
+    <t>Auxiliary Power Supply Filtering</t>
+  </si>
+  <si>
+    <t>Lighting Sensor</t>
+  </si>
+  <si>
+    <t>Red LEDs</t>
+  </si>
+  <si>
+    <t>Controls Surface Illumination</t>
+  </si>
+  <si>
+    <t>LiPo Battery</t>
+  </si>
+  <si>
+    <t>Main Power Source for the Robot</t>
+  </si>
+  <si>
+    <t>PC817 Optocoupler</t>
+  </si>
+  <si>
+    <t>Optocoupler</t>
+  </si>
+  <si>
+    <t>Protects the Control Electronics from Noise and Voltage Spikes</t>
+  </si>
+  <si>
+    <t>Convex Mirror</t>
+  </si>
+  <si>
+    <t>Expands the Camera’s Field of View</t>
+  </si>
+  <si>
+    <t>Tactile Switch</t>
+  </si>
+  <si>
+    <t>Quick System Function Activation</t>
+  </si>
+  <si>
+    <t>Motor Bell Housing</t>
+  </si>
+  <si>
+    <t>4 mm Shaft Coupler</t>
+  </si>
+  <si>
+    <t>Mechanical Coupling Between Wheel and Motor</t>
+  </si>
+  <si>
+    <t>Solenoid Control</t>
+  </si>
+  <si>
+    <t>IRLZ44N MOSFET</t>
+  </si>
+  <si>
+    <t>Electronic Switching of the Power System</t>
+  </si>
+  <si>
+    <t>KRE Connector</t>
+  </si>
+  <si>
+    <t>2-Position Terminal Block, 5 mm Pitch</t>
+  </si>
+  <si>
+    <t>Facilitates Removable Electronic Connections</t>
+  </si>
+  <si>
+    <t>Schottky Diode</t>
+  </si>
+  <si>
+    <t>Reverse Current Protection</t>
+  </si>
+  <si>
+    <t>4-Pin Female KK Connector</t>
+  </si>
+  <si>
+    <t>2.5 mm 4-Pin Female Connector</t>
+  </si>
+  <si>
+    <t>Communication Between Sensors and Boards</t>
+  </si>
+  <si>
+    <t>220 Ω Resistor</t>
+  </si>
+  <si>
+    <t>220 Ω 1/4-Watt Resistor</t>
+  </si>
+  <si>
+    <t>Electrical Current Limiting</t>
+  </si>
+  <si>
+    <t>10 Ω Resistor</t>
+  </si>
+  <si>
+    <t>10 Ω 1/4-Watt Resistor</t>
+  </si>
+  <si>
+    <t>Electronic Signal Conditioning and Protection</t>
+  </si>
+  <si>
+    <t>2-Pin Male KK Connector</t>
+  </si>
+  <si>
+    <t>2.54 mm 180° Male Header</t>
+  </si>
+  <si>
+    <t>Power and Signal Connection</t>
+  </si>
+  <si>
+    <t>2-Pin Female KK Connector</t>
+  </si>
+  <si>
+    <t>2.5 mm 2-Pin Female Connector</t>
+  </si>
+  <si>
+    <t>Removable Interface Between Modules</t>
+  </si>
+  <si>
+    <t>Limit Switch</t>
+  </si>
+  <si>
+    <t>Mechanical Position Detection</t>
+  </si>
+  <si>
+    <t>Carbon Film Resistor</t>
+  </si>
+  <si>
+    <t>100 Ω 1/4-Watt Resistor</t>
+  </si>
+  <si>
+    <t>Voltage Control and Division</t>
+  </si>
+  <si>
+    <t>Actuator</t>
+  </si>
+  <si>
+    <t>12V Mini Solenoid Electric Lock</t>
+  </si>
+  <si>
+    <t>Electromagnetic Mechanical Actuation</t>
+  </si>
+  <si>
+    <t>BC327 Transistor</t>
+  </si>
+  <si>
+    <t>Electronic Amplification and Switching</t>
+  </si>
+  <si>
+    <t>BC337 Transistor</t>
+  </si>
+  <si>
+    <t>Signal and Actuation Control</t>
+  </si>
+  <si>
+    <t>100 kΩ Resistor</t>
+  </si>
+  <si>
+    <t>100 kΩ Resistor × 1/4 W</t>
+  </si>
+  <si>
+    <t>Pull-Up and Logic Stabilization</t>
+  </si>
+  <si>
+    <t>Ceramic Disc Capacitor</t>
+  </si>
+  <si>
+    <t>100 nF, 50 V Capacitor</t>
+  </si>
+  <si>
+    <t>High-Frequency Noise Filtering</t>
+  </si>
+  <si>
+    <t>Electrolytic Capacitor</t>
+  </si>
+  <si>
+    <t>470 µF, 25 V Capacitor</t>
+  </si>
+  <si>
+    <t>Power Supply Stabilization</t>
+  </si>
+  <si>
+    <t>20A 60V Rectifier Diode</t>
+  </si>
+  <si>
+    <t>Rectification and Overcurrent Protection</t>
+  </si>
+  <si>
+    <t>Acrylic Tube</t>
+  </si>
+  <si>
+    <t>Ø60 × 2 mm Wall Thickness × 1 m</t>
+  </si>
+  <si>
+    <t>Structural Protection and Finishing</t>
+  </si>
+  <si>
+    <t>4-Pin Male KK Connector</t>
+  </si>
+  <si>
+    <t>2.5 mm Male Connector, 4-Pin</t>
+  </si>
+  <si>
+    <t>5D-9 NTC Thermistor (5 Ω)</t>
+  </si>
+  <si>
+    <t>5 Ω NTC Thermistor, 9 mm</t>
+  </si>
+  <si>
+    <t>Thermistor for Main Power Supply</t>
+  </si>
+  <si>
+    <t>Total Cost per Robot:</t>
+  </si>
+  <si>
+    <t>Total Project Cost:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="[$$-409]#,##0.00"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -635,6 +1099,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -744,7 +1214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -783,6 +1253,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -790,7 +1269,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="52">
     <dxf>
       <font>
         <sz val="12"/>
@@ -1499,6 +1978,714 @@
         </horizontal>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+        <name val="Arial"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+        <name val="Arial"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+        <name val="Arial"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+        <name val="Arial"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+        <name val="Arial"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+        <name val="Arial"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+        <name val="Arial"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+        <name val="Arial"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+        <name val="Arial"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+        <name val="Arial"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+        <name val="Arial"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+        <name val="Arial"/>
+      </font>
+      <border>
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+        <name val="Arial"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+        <name val="Arial"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -1513,20 +2700,40 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8D33B183-2A59-4AD2-BAA6-87591A87C8F9}" name="Tabela1" displayName="Tabela1" ref="A3:L54" headerRowCount="0" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8D33B183-2A59-4AD2-BAA6-87591A87C8F9}" name="Tabela1" displayName="Tabela1" ref="A3:L54" headerRowCount="0" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50">
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{6139B640-5C99-45D6-9162-3D6032709B7C}" name="Coluna1" headerRowDxfId="23" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{B9DA0266-7022-4386-955C-367F63E0A3C5}" name="Coluna2" headerRowDxfId="21" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{172393A5-EA1E-4BB9-BCBF-86989582815F}" name="Coluna3" headerRowDxfId="19" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{690BFF48-771D-4ED4-9781-7E4112C25C04}" name="Coluna4" headerRowDxfId="17" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{CCDCE4DA-66EF-418A-B42F-985218F284F8}" name="Coluna5" headerRowDxfId="15" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{039748C9-9D50-4C97-857B-E66EFDFD962C}" name="Coluna6" headerRowDxfId="13" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{8426603C-D619-4CC1-8490-CFEBF1182D02}" name="Coluna7" headerRowDxfId="11" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{DB8A53A2-F1F2-4702-ACB0-FF4862B3FF91}" name="Coluna8" headerRowDxfId="9" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{3C8C808F-C983-4AA4-9329-A7A3433C457F}" name="Coluna9" headerRowDxfId="7" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{BD45B948-3DF0-4D26-A07C-CD0C18062071}" name="Coluna10" headerRowDxfId="5" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{5A85A09C-4033-45BC-951F-8C9FDFD5C933}" name="Coluna11" headerRowDxfId="3" dataDxfId="2"/>
-    <tableColumn id="12" xr3:uid="{4B1847DA-67AB-4BA2-A45A-7DEC1678F262}" name="Coluna12" headerRowDxfId="1" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{6139B640-5C99-45D6-9162-3D6032709B7C}" name="Coluna1" headerRowDxfId="49" dataDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{B9DA0266-7022-4386-955C-367F63E0A3C5}" name="Coluna2" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="3" xr3:uid="{172393A5-EA1E-4BB9-BCBF-86989582815F}" name="Coluna3" headerRowDxfId="45" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{690BFF48-771D-4ED4-9781-7E4112C25C04}" name="Coluna4" headerRowDxfId="43" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{CCDCE4DA-66EF-418A-B42F-985218F284F8}" name="Coluna5" headerRowDxfId="41" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{039748C9-9D50-4C97-857B-E66EFDFD962C}" name="Coluna6" headerRowDxfId="39" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{8426603C-D619-4CC1-8490-CFEBF1182D02}" name="Coluna7" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="8" xr3:uid="{DB8A53A2-F1F2-4702-ACB0-FF4862B3FF91}" name="Coluna8" headerRowDxfId="35" dataDxfId="34"/>
+    <tableColumn id="9" xr3:uid="{3C8C808F-C983-4AA4-9329-A7A3433C457F}" name="Coluna9" headerRowDxfId="33" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{BD45B948-3DF0-4D26-A07C-CD0C18062071}" name="Coluna10" headerRowDxfId="31" dataDxfId="30"/>
+    <tableColumn id="11" xr3:uid="{5A85A09C-4033-45BC-951F-8C9FDFD5C933}" name="Coluna11" headerRowDxfId="29" dataDxfId="28"/>
+    <tableColumn id="12" xr3:uid="{4B1847DA-67AB-4BA2-A45A-7DEC1678F262}" name="Coluna12" headerRowDxfId="27" dataDxfId="26"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{485AD6C4-9EBE-4351-9F42-9E1A2799972B}" name="Tabela14" displayName="Tabela14" ref="A3:L54" headerRowCount="0" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{6643B6F5-5E32-4014-A08F-39D2B75625F3}" name="Coluna1" headerRowDxfId="23" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{4F804A6E-8AF6-4F1A-AC1B-30A4DC058DC5}" name="Coluna2" headerRowDxfId="21" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{F47F6D96-B92F-4D2B-A547-B0CF25D9A964}" name="Coluna3" headerRowDxfId="19" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{38842279-9873-476D-B23F-5F3F5F421FB4}" name="Coluna4" headerRowDxfId="17" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{E9D17367-3842-43A4-9D00-F9BE52F16F19}" name="Coluna5" headerRowDxfId="15" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{28028496-D6B2-4212-817C-ED8F6FF8CA9C}" name="Coluna6" headerRowDxfId="13" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{BD1DA1DB-4375-4B04-9EF2-BB543E2FA956}" name="Coluna7" headerRowDxfId="11" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{0247F5F6-44D8-4DE5-8796-A17AD93B1B69}" name="Coluna8" headerRowDxfId="9" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{23608D92-C39D-479D-A038-AF2D393F87AD}" name="Coluna9" headerRowDxfId="7" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{8622D4CE-F38A-4F42-8C88-17674F1D0B45}" name="Coluna10" headerRowDxfId="5" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{336D165C-00AE-4B9B-A5B7-D9A41CED0D6F}" name="Coluna11" headerRowDxfId="3" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{CF3E562B-B577-4A20-9FB0-F42C8AA363C8}" name="Coluna12" headerRowDxfId="1" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1847,20 +3054,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
     </row>
     <row r="2" spans="1:12" ht="21.75" hidden="1" customHeight="1"/>
     <row r="3" spans="1:12" ht="15.75">
@@ -1990,7 +3197,9 @@
       <c r="E6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="3"/>
+      <c r="F6" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="G6" s="3" t="s">
         <v>17</v>
       </c>
@@ -2256,7 +3465,9 @@
       <c r="E13" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="G13" s="3" t="s">
         <v>17</v>
       </c>
@@ -2274,7 +3485,7 @@
         <v>18</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75">
@@ -2282,16 +3493,16 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>41</v>
@@ -2312,7 +3523,7 @@
         <v>18</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75">
@@ -2320,19 +3531,19 @@
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>17</v>
@@ -2350,7 +3561,7 @@
         <v>18</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75">
@@ -2358,18 +3569,20 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D16" s="2">
         <v>1</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F16" s="3"/>
+        <v>69</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="G16" s="3" t="s">
         <v>17</v>
       </c>
@@ -2386,7 +3599,7 @@
         <v>18</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15.75">
@@ -2394,19 +3607,19 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D17" s="10">
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>17</v>
@@ -2425,7 +3638,7 @@
         <v>18</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15.75">
@@ -2433,19 +3646,19 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D18" s="2">
         <v>1</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>17</v>
@@ -2464,7 +3677,7 @@
         <v>18</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15.75">
@@ -2472,19 +3685,19 @@
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D19" s="10">
         <v>1</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>17</v>
@@ -2503,7 +3716,7 @@
         <v>18</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15.75">
@@ -2511,19 +3724,19 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D20" s="2">
         <v>1</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>17</v>
@@ -2542,7 +3755,7 @@
         <v>18</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15.75">
@@ -2550,19 +3763,19 @@
         <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D21" s="10">
         <v>32</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>17</v>
@@ -2581,7 +3794,7 @@
         <v>18</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15.75">
@@ -2589,16 +3802,16 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D22" s="10">
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>41</v>
@@ -2619,7 +3832,7 @@
         <v>18</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15.75">
@@ -2627,16 +3840,16 @@
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D23" s="10">
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>32</v>
@@ -2658,7 +3871,7 @@
         <v>18</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15.75">
@@ -2666,16 +3879,16 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D24" s="10">
         <v>2</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>32</v>
@@ -2697,7 +3910,7 @@
         <v>18</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75">
@@ -2705,14 +3918,14 @@
         <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D25" s="10"/>
       <c r="E25" s="19" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>32</v>
@@ -2731,7 +3944,7 @@
         <v>18</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15.75">
@@ -2739,16 +3952,16 @@
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D26" s="10">
         <v>1</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>23</v>
@@ -2770,7 +3983,7 @@
         <v>18</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15.75">
@@ -2778,19 +3991,19 @@
         <v>24</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D27" s="10">
         <v>32</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>17</v>
@@ -2809,7 +4022,7 @@
         <v>18</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15.75">
@@ -2817,16 +4030,16 @@
         <v>25</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D28" s="10">
         <v>1</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>23</v>
@@ -2848,7 +4061,7 @@
         <v>18</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="15.75">
@@ -2859,13 +4072,13 @@
         <v>29</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D29" s="10">
         <v>1</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>23</v>
@@ -2886,7 +4099,7 @@
         <v>18</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15.75">
@@ -2897,7 +4110,7 @@
         <v>55</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D30" s="10">
         <v>1</v>
@@ -2905,7 +4118,9 @@
       <c r="E30" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F30" s="1"/>
+      <c r="F30" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="G30" s="1" t="s">
         <v>17</v>
       </c>
@@ -2918,7 +4133,7 @@
         <v>18</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15.75">
@@ -2926,16 +4141,16 @@
         <v>28</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D31" s="10">
         <v>3</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>41</v>
@@ -2957,7 +4172,7 @@
         <v>18</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15.75">
@@ -2968,13 +4183,13 @@
         <v>20</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D32" s="10">
         <v>4</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>41</v>
@@ -2996,7 +4211,7 @@
         <v>18</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="15.75">
@@ -3004,16 +4219,16 @@
         <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D33" s="10">
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>32</v>
@@ -3035,7 +4250,7 @@
         <v>18</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="15.75">
@@ -3043,16 +4258,16 @@
         <v>31</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D34" s="10">
         <v>6</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>23</v>
@@ -3074,7 +4289,7 @@
         <v>18</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="15.75">
@@ -3082,19 +4297,19 @@
         <v>32</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D35" s="10">
         <v>3</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>17</v>
@@ -3113,7 +4328,7 @@
         <v>18</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="15.75">
@@ -3121,19 +4336,19 @@
         <v>33</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D36" s="10">
         <v>4</v>
       </c>
       <c r="E36" s="19" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>17</v>
@@ -3152,7 +4367,7 @@
         <v>18</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="15.75">
@@ -3163,16 +4378,16 @@
         <v>29</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D37" s="10">
         <v>32</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>17</v>
@@ -3191,7 +4406,7 @@
         <v>18</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15.75">
@@ -3202,16 +4417,16 @@
         <v>29</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D38" s="10">
         <v>32</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>17</v>
@@ -3230,7 +4445,7 @@
         <v>18</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="15.75">
@@ -3238,19 +4453,19 @@
         <v>36</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D39" s="10">
         <v>2</v>
       </c>
       <c r="E39" s="19" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>17</v>
@@ -3269,7 +4484,7 @@
         <v>18</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="15.75">
@@ -3277,19 +4492,19 @@
         <v>37</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D40" s="10">
         <v>2</v>
       </c>
       <c r="E40" s="19" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>17</v>
@@ -3308,7 +4523,7 @@
         <v>18</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="15.75">
@@ -3316,19 +4531,19 @@
         <v>38</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D41" s="10">
         <v>1</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>17</v>
@@ -3347,7 +4562,7 @@
         <v>18</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="15.75">
@@ -3358,16 +4573,16 @@
         <v>29</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D42" s="10">
         <v>1</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>17</v>
@@ -3386,7 +4601,7 @@
         <v>18</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="15.75">
@@ -3394,19 +4609,19 @@
         <v>40</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D43" s="10">
         <v>1</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>17</v>
@@ -3425,7 +4640,7 @@
         <v>18</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="15.75">
@@ -3436,16 +4651,16 @@
         <v>29</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D44" s="10">
         <v>1</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>17</v>
@@ -3464,7 +4679,7 @@
         <v>18</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="15.75">
@@ -3475,16 +4690,16 @@
         <v>29</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D45" s="10">
         <v>1</v>
       </c>
       <c r="E45" s="19" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>17</v>
@@ -3503,7 +4718,7 @@
         <v>18</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="15.75">
@@ -3514,16 +4729,16 @@
         <v>29</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D46" s="10">
         <v>40</v>
       </c>
       <c r="E46" s="19" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>17</v>
@@ -3542,7 +4757,7 @@
         <v>18</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="15.75">
@@ -3550,16 +4765,16 @@
         <v>44</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D47" s="10">
         <v>20</v>
       </c>
       <c r="E47" s="19" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>32</v>
@@ -3581,7 +4796,7 @@
         <v>18</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="15.75">
@@ -3589,16 +4804,16 @@
         <v>45</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D48" s="10">
         <v>7</v>
       </c>
       <c r="E48" s="19" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>32</v>
@@ -3620,7 +4835,7 @@
         <v>18</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="15.75">
@@ -3628,22 +4843,22 @@
         <v>46</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D49" s="10">
         <v>1</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>32</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>24</v>
@@ -3659,7 +4874,7 @@
         <v>18</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="15.75">
@@ -3670,19 +4885,19 @@
         <v>13</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D50" s="10">
         <v>1</v>
       </c>
       <c r="E50" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G50" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>167</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>24</v>
@@ -3698,7 +4913,7 @@
         <v>18</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="15.75">
@@ -3706,19 +4921,19 @@
         <v>48</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D51" s="10">
         <v>4</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>17</v>
@@ -3737,7 +4952,7 @@
         <v>18</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="15.75">
@@ -3745,20 +4960,22 @@
         <v>49</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D52" s="10">
         <v>1</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="F52" s="1"/>
+        <v>179</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="G52" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>24</v>
@@ -3773,7 +4990,7 @@
         <v>18</v>
       </c>
       <c r="L52" s="23" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="15.75">
@@ -3786,7 +5003,7 @@
       <c r="G53" s="9"/>
       <c r="H53" s="9"/>
       <c r="I53" s="18" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="J53" s="20">
         <f>SUM(J4:J52)</f>
@@ -3805,7 +5022,7 @@
       <c r="G54" s="9"/>
       <c r="H54" s="9"/>
       <c r="I54" s="11" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="J54" s="8">
         <f>J53*2</f>
@@ -3840,4 +5057,2029 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13F7A51C-28F1-4A25-8BAA-9E4046E0CA87}">
+  <dimension ref="A1:L59"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="67.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="15.75">
+      <c r="A1" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+    </row>
+    <row r="2" spans="1:12" hidden="1"/>
+    <row r="3" spans="1:12" ht="15.75">
+      <c r="A3" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="L3" s="16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15.75">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I4" s="25"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15.75">
+      <c r="A5" s="2">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" s="25">
+        <v>16.96</v>
+      </c>
+      <c r="J5" s="26">
+        <f>I5*4</f>
+        <v>67.84</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15.75">
+      <c r="A6" s="2">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D6" s="2">
+        <v>4</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15.75">
+      <c r="A7" s="2">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="2">
+        <v>4</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="25">
+        <v>17.98</v>
+      </c>
+      <c r="J7" s="26">
+        <f>I7*4</f>
+        <v>71.92</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75">
+      <c r="A8" s="2">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="25">
+        <v>3.58</v>
+      </c>
+      <c r="J8" s="26">
+        <f>I8*2</f>
+        <v>7.16</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15.75">
+      <c r="A9" s="2">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="2">
+        <v>12</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" s="25">
+        <v>2.38</v>
+      </c>
+      <c r="J9" s="26">
+        <f>I9*12</f>
+        <v>28.56</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75">
+      <c r="A10" s="2">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" s="25">
+        <v>1.38</v>
+      </c>
+      <c r="J10" s="26">
+        <f>I10*2</f>
+        <v>2.76</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.75">
+      <c r="A11" s="2">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" s="25">
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="J11" s="26">
+        <f>I11*1</f>
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15.75">
+      <c r="A12" s="2">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D12" s="2">
+        <v>4</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="25">
+        <v>1.74</v>
+      </c>
+      <c r="J12" s="26">
+        <f>I12*4</f>
+        <v>6.96</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.75">
+      <c r="A13" s="2">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" s="25">
+        <v>398.18</v>
+      </c>
+      <c r="J13" s="26">
+        <f>I13*1</f>
+        <v>398.18</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15.75">
+      <c r="A14" s="2">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I14" s="25">
+        <v>4.7519999999999998</v>
+      </c>
+      <c r="J14" s="26">
+        <v>23</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.75">
+      <c r="A15" s="2">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" s="25">
+        <v>0.6</v>
+      </c>
+      <c r="J15" s="26">
+        <v>3</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15.75">
+      <c r="A16" s="2">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I16" s="25">
+        <v>1.708</v>
+      </c>
+      <c r="J16" s="26">
+        <v>8.5399999999999991</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15.75">
+      <c r="A17" s="2">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D17" s="10">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="I17" s="27">
+        <v>31.37</v>
+      </c>
+      <c r="J17" s="27">
+        <f>I17*1</f>
+        <v>31.37</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="15.75">
+      <c r="A18" s="2">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I18" s="26">
+        <v>36.103999999999999</v>
+      </c>
+      <c r="J18" s="26">
+        <f>I18*1</f>
+        <v>36.103999999999999</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="15.75">
+      <c r="A19" s="2">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="D19" s="10">
+        <v>1</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="I19" s="27">
+        <v>29.731999999999999</v>
+      </c>
+      <c r="J19" s="27">
+        <f>I19*1</f>
+        <v>29.731999999999999</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15.75">
+      <c r="A20" s="2">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I20" s="26">
+        <v>38.252000000000002</v>
+      </c>
+      <c r="J20" s="26">
+        <f>I20*1</f>
+        <v>38.252000000000002</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="15.75">
+      <c r="A21" s="2">
+        <v>18</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="D21" s="10">
+        <v>32</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I21" s="27">
+        <v>0.08</v>
+      </c>
+      <c r="J21" s="27">
+        <f>I21*32</f>
+        <v>2.56</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="15.75">
+      <c r="A22" s="2">
+        <v>19</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D22" s="10">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I22" s="27">
+        <v>1.556</v>
+      </c>
+      <c r="J22" s="27">
+        <v>8.5</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="15.75">
+      <c r="A23" s="2">
+        <v>20</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D23" s="10">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I23" s="27">
+        <v>1.78</v>
+      </c>
+      <c r="J23" s="27">
+        <f>I23*1</f>
+        <v>1.78</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15.75">
+      <c r="A24" s="2">
+        <v>21</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D24" s="10">
+        <v>2</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I24" s="27">
+        <v>1.38</v>
+      </c>
+      <c r="J24" s="27">
+        <f>I24*2</f>
+        <v>2.76</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="15.75">
+      <c r="A25" s="2">
+        <v>22</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D25" s="10"/>
+      <c r="E25" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I25" s="27">
+        <v>0.05</v>
+      </c>
+      <c r="J25" s="27"/>
+      <c r="K25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="15.75">
+      <c r="A26" s="2">
+        <v>23</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D26" s="10">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26" s="27">
+        <v>0.74</v>
+      </c>
+      <c r="J26" s="27">
+        <f>I26*1</f>
+        <v>0.74</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="15.75">
+      <c r="A27" s="2">
+        <v>24</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D27" s="10">
+        <v>32</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I27" s="27">
+        <v>2.4E-2</v>
+      </c>
+      <c r="J27" s="27">
+        <f>I27*32</f>
+        <v>0.76800000000000002</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="15.75">
+      <c r="A28" s="2">
+        <v>25</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D28" s="10">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" s="27">
+        <v>67.965999999999994</v>
+      </c>
+      <c r="J28" s="27">
+        <f>I28*1</f>
+        <v>67.965999999999994</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="15.75">
+      <c r="A29" s="2">
+        <v>26</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D29" s="10">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I29" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="J29" s="27">
+        <v>1</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="15.75">
+      <c r="A30" s="2">
+        <v>27</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D30" s="10">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="I30" s="27"/>
+      <c r="J30" s="27"/>
+      <c r="K30" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="15.75">
+      <c r="A31" s="2">
+        <v>28</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="D31" s="10">
+        <v>3</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31" s="27">
+        <v>0.312</v>
+      </c>
+      <c r="J31" s="27">
+        <f>I31*3</f>
+        <v>0.93599999999999994</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="15.75">
+      <c r="A32" s="2">
+        <v>29</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="D32" s="10">
+        <v>4</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" s="27">
+        <v>3.9420000000000002</v>
+      </c>
+      <c r="J32" s="27">
+        <f>I32*4</f>
+        <v>15.768000000000001</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="15.75">
+      <c r="A33" s="2">
+        <v>30</v>
+      </c>
+      <c r="B33" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D33" s="10">
+        <v>1</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I33" s="27">
+        <v>1.58</v>
+      </c>
+      <c r="J33" s="27">
+        <f>I33*1</f>
+        <v>1.58</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="15.75">
+      <c r="A34" s="2">
+        <v>31</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="D34" s="10">
+        <v>6</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I34" s="27">
+        <v>0.15</v>
+      </c>
+      <c r="J34" s="27">
+        <f>I34*6</f>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="15.75">
+      <c r="A35" s="2">
+        <v>32</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D35" s="10">
+        <v>3</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35" s="27">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="J35" s="27">
+        <f>I35*3</f>
+        <v>0.14400000000000002</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="15.75">
+      <c r="A36" s="2">
+        <v>33</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="D36" s="10">
+        <v>4</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36" s="27">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="J36" s="27">
+        <f>I36*4</f>
+        <v>0.152</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="15.75">
+      <c r="A37" s="2">
+        <v>34</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="D37" s="10">
+        <v>32</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I37" s="27">
+        <v>0.01</v>
+      </c>
+      <c r="J37" s="27">
+        <f>I37*32</f>
+        <v>0.32</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="15.75">
+      <c r="A38" s="2">
+        <v>35</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="D38" s="10">
+        <v>32</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I38" s="27">
+        <v>0.01</v>
+      </c>
+      <c r="J38" s="27">
+        <f>I38*32</f>
+        <v>0.32</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="15.75">
+      <c r="A39" s="2">
+        <v>36</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="D39" s="10">
+        <v>2</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>296</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I39" s="27">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="J39" s="27">
+        <f>I39*2</f>
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="15.75">
+      <c r="A40" s="2">
+        <v>37</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="D40" s="10">
+        <v>2</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I40" s="27">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="J40" s="27">
+        <f>I40*2</f>
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="15.75">
+      <c r="A41" s="2">
+        <v>38</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="D41" s="10">
+        <v>1</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I41" s="27">
+        <v>0.53</v>
+      </c>
+      <c r="J41" s="27">
+        <f>I41*1</f>
+        <v>0.53</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="15.75">
+      <c r="A42" s="2">
+        <v>39</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="D42" s="10">
+        <v>1</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42" s="27">
+        <v>1.2E-2</v>
+      </c>
+      <c r="J42" s="27">
+        <f>I42*1</f>
+        <v>1.2E-2</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="15.75">
+      <c r="A43" s="2">
+        <v>40</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="D43" s="10">
+        <v>1</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I43" s="27">
+        <v>8.82</v>
+      </c>
+      <c r="J43" s="27">
+        <f>I43*1</f>
+        <v>8.82</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="15.75">
+      <c r="A44" s="2">
+        <v>41</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="D44" s="10">
+        <v>1</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I44" s="27">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="J44" s="27">
+        <f>I44*1</f>
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="15.75">
+      <c r="A45" s="2">
+        <v>42</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="D45" s="10">
+        <v>1</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I45" s="27">
+        <v>0.06</v>
+      </c>
+      <c r="J45" s="27">
+        <f>I45*1</f>
+        <v>0.06</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="15.75">
+      <c r="A46" s="2">
+        <v>43</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C46" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="D46" s="10">
+        <v>40</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I46" s="27">
+        <v>1.2E-2</v>
+      </c>
+      <c r="J46" s="27">
+        <f>I46*40</f>
+        <v>0.48</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="15.75">
+      <c r="A47" s="2">
+        <v>44</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="D47" s="10">
+        <v>20</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>317</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47" s="27">
+        <v>0.02</v>
+      </c>
+      <c r="J47" s="27">
+        <f>I47*20</f>
+        <v>0.4</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="15.75">
+      <c r="A48" s="2">
+        <v>45</v>
+      </c>
+      <c r="B48" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="D48" s="10">
+        <v>7</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I48" s="27">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J48" s="27">
+        <f>I48*7</f>
+        <v>0.49000000000000005</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="15.75">
+      <c r="A49" s="2">
+        <v>46</v>
+      </c>
+      <c r="B49" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="D49" s="10">
+        <v>1</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I49" s="27">
+        <v>1.38</v>
+      </c>
+      <c r="J49" s="27">
+        <f>I49*1</f>
+        <v>1.38</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="15.75">
+      <c r="A50" s="2">
+        <v>47</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="D50" s="10">
+        <v>1</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I50" s="27">
+        <v>63</v>
+      </c>
+      <c r="J50" s="27">
+        <f>I50*1</f>
+        <v>63</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="15.75">
+      <c r="A51" s="2">
+        <v>48</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="D51" s="10">
+        <v>4</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I51" s="27">
+        <v>0.06</v>
+      </c>
+      <c r="J51" s="27">
+        <f>I51*4</f>
+        <v>0.24</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="15.75">
+      <c r="A52" s="22">
+        <v>49</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="D52" s="10">
+        <v>1</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I52" s="27">
+        <v>0.74</v>
+      </c>
+      <c r="J52" s="27">
+        <v>3.7</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L52" s="23" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="15.75">
+      <c r="A53" s="9"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="9"/>
+      <c r="H53" s="9"/>
+      <c r="I53" s="28" t="s">
+        <v>332</v>
+      </c>
+      <c r="J53" s="29">
+        <f>SUM(J4:J52)</f>
+        <v>943.82400000000007</v>
+      </c>
+      <c r="K53" s="9"/>
+      <c r="L53" s="9"/>
+    </row>
+    <row r="54" spans="1:12" ht="15.75">
+      <c r="A54" s="9"/>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
+      <c r="I54" s="30" t="s">
+        <v>333</v>
+      </c>
+      <c r="J54" s="27">
+        <f>J53*2</f>
+        <v>1887.6480000000001</v>
+      </c>
+      <c r="K54" s="9"/>
+      <c r="L54" s="9"/>
+    </row>
+    <row r="55" spans="1:12" ht="15.75">
+      <c r="A55" s="9"/>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9"/>
+      <c r="K55" s="9"/>
+      <c r="L55" s="9"/>
+    </row>
+    <row r="59" spans="1:12" ht="15.75">
+      <c r="E59" s="15"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>